--- a/R_analysis/output/tables/Tabela_Moran_Global.xlsx
+++ b/R_analysis/output/tables/Tabela_Moran_Global.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sífilis Gestacional</t>
+          <t>Sífilis Gestational</t>
         </is>
       </c>
       <c r="B2">
@@ -403,7 +403,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sífilis Congênita</t>
+          <t>Sífilis Congenital</t>
         </is>
       </c>
     </row>
